--- a/server1/myfile.xlsx
+++ b/server1/myfile.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,7 +414,7 @@
         <v>Select Disabled Passenger Concession</v>
       </c>
       <c r="B5" t="str">
-        <v>Handicapped,Mentally Retarded,Blind,Deaf Dumb</v>
+        <v>Handicapped , Mentally Retarded , Blind , Deaf Dumb,Handicapped and Mentally Retarded ,Handicapped and Blind ,Handicapped and Deaf Dumb, Mentally Retarded and Blind , Mentally Retarded and Deaf Dumb, Blind and Deaf Dumb,Handicapped and Mentally Retarded and Blind ,Handicapped and Mentally Retarded and Deaf Dumb,Handicapped and Blind and Deaf Dumb, Mentally Retarded and Blind and Deaf Dumb,Handicapped and Mentally Retarded and Blind and Deaf Dumb</v>
       </c>
     </row>
     <row r="6">
@@ -422,7 +422,7 @@
         <v>Select Patient Concession</v>
       </c>
       <c r="B6" t="str">
-        <v>Cancer,heart,kidney,thalassemia,TB,AIDS,Haemophilia,Leprosy</v>
+        <v>Cancer , heart , kidney , thalassemia , TB , AIDS , Haemophilia , Leprosy,Cancer and heart ,Cancer and kidney ,Cancer and thalassemia ,Cancer and TB ,Cancer and AIDS ,Cancer and Haemophilia ,Cancer and Leprosy, heart and kidney , heart and thalassemia , heart and TB , heart and AIDS , heart and Haemophilia , heart and Leprosy, kidney and thalassemia , kidney and TB , kidney and AIDS , kidney and Haemophilia , kidney and Leprosy, thalassemia and TB , thalassemia and AIDS , thalassemia and Haemophilia , thalassemia and Leprosy, TB and AIDS , TB and Haemophilia , TB and Leprosy, AIDS and Haemophilia , AIDS and Leprosy, Haemophilia and Leprosy,Cancer and heart and kidney ,Cancer and heart and thalassemia ,Cancer and heart and TB ,Cancer and heart and AIDS ,Cancer and heart and Haemophilia ,Cancer and heart and Leprosy,Cancer and kidney and thalassemia ,Cancer and kidney and TB ,Cancer and kidney and AIDS ,Cancer and kidney and Haemophilia ,Cancer and kidney and Leprosy,Cancer and thalassemia and TB ,Cancer and thalassemia and AIDS ,Cancer and thalassemia and Haemophilia ,Cancer and thalassemia and Leprosy,Cancer and TB and AIDS ,Cancer and TB and Haemophilia ,Cancer and TB and Leprosy,Cancer and AIDS and Haemophilia ,Cancer and AIDS and Leprosy,Cancer and Haemophilia and Leprosy, heart and kidney and thalassemia , heart and kidney and TB , heart and kidney and AIDS , heart and kidney and Haemophilia , heart and kidney and Leprosy, heart and thalassemia and TB , heart and thalassemia and AIDS , heart and thalassemia and Haemophilia , heart and thalassemia and Leprosy, heart and TB and AIDS , heart and TB and Haemophilia , heart and TB and Leprosy, heart and AIDS and Haemophilia , heart and AIDS and Leprosy, heart and Haemophilia and Leprosy, kidney and thalassemia and TB , kidney and thalassemia and AIDS , kidney and thalassemia and Haemophilia , kidney and thalassemia and Leprosy, kidney and TB and AIDS , kidney and TB and Haemophilia , kidney and TB and Leprosy, kidney and AIDS and Haemophilia , kidney and AIDS and Leprosy, kidney and Haemophilia and Leprosy, thalassemia and TB and AIDS , thalassemia and TB and Haemophilia , thalassemia and TB and Leprosy, thalassemia and AIDS and Haemophilia , thalassemia and AIDS and Leprosy, thalassemia and Haemophilia and Leprosy, TB and AIDS and Haemophilia , TB and AIDS and Leprosy, TB and Haemophilia and Leprosy, AIDS and Haemophilia and Leprosy,Cancer and heart and kidney and thalassemia ,Cancer and heart and kidney and TB ,Cancer and heart and kidney and AIDS ,Cancer and heart and kidney and Haemophilia ,Cancer and heart and kidney and Leprosy,Cancer and heart and thalassemia and TB ,Cancer and heart and thalassemia and AIDS ,Cancer and heart and thalassemia and Haemophilia ,Cancer and heart and thalassemia and Leprosy,Cancer and heart and TB and AIDS ,Cancer and heart and TB and Haemophilia ,Cancer and heart and TB and Leprosy,Cancer and heart and AIDS and Haemophilia ,Cancer and heart and AIDS and Leprosy,Cancer and heart and Haemophilia and Leprosy,Cancer and kidney and thalassemia and TB ,Cancer and kidney and thalassemia and AIDS ,Cancer and kidney and thalassemia and Haemophilia ,Cancer and kidney and thalassemia and Leprosy,Cancer and kidney and TB and AIDS ,Cancer and kidney and TB and Haemophilia ,Cancer and kidney and TB and Leprosy,Cancer and kidney and AIDS and Haemophilia ,Cancer and kidney and AIDS and Leprosy,Cancer and kidney and Haemophilia and Leprosy,Cancer and thalassemia and TB and AIDS ,Cancer and thalassemia and TB and Haemophilia ,Cancer and thalassemia and TB and Leprosy,Cancer and thalassemia and AIDS and Haemophilia ,Cancer and thalassemia and AIDS and Leprosy,Cancer and thalassemia and Haemophilia and Leprosy,Cancer and TB and AIDS and Haemophilia ,Cancer and TB and AIDS and Leprosy,Cancer and TB and Haemophilia and Leprosy,Cancer and AIDS and Haemophilia and Leprosy, heart and kidney and thalassemia and TB , heart and kidney and thalassemia and AIDS , heart and kidney and thalassemia and Haemophilia , heart and kidney and thalassemia and Leprosy, heart and kidney and TB and AIDS , heart and kidney and TB and Haemophilia , heart and kidney and TB and Leprosy, heart and kidney and AIDS and Haemophilia , heart and kidney and AIDS and Leprosy, heart and kidney and Haemophilia and Leprosy, heart and thalassemia and TB and AIDS , heart and thalassemia and TB and Haemophilia , heart and thalassemia and TB and Leprosy, heart and thalassemia and AIDS and Haemophilia , heart and thalassemia and AIDS and Leprosy, heart and thalassemia and Haemophilia and Leprosy, heart and TB and AIDS and Haemophilia , heart and TB and AIDS and Leprosy, heart and TB and Haemophilia and Leprosy, heart and AIDS and Haemophilia and Leprosy, kidney and thalassemia and TB and AIDS , kidney and thalassemia and TB and Haemophilia , kidney and thalassemia and TB and Leprosy, kidney and thalassemia and AIDS and Haemophilia , kidney and thalassemia and AIDS and Leprosy, kidney and thalassemia and Haemophilia and Leprosy, kidney and TB and AIDS and Haemophilia , kidney and TB and AIDS and Leprosy, kidney and TB and Haemophilia and Leprosy, kidney and AIDS and Haemophilia and Leprosy, thalassemia and TB and AIDS and Haemophilia , thalassemia and TB and AIDS and Leprosy, thalassemia and TB and Haemophilia and Leprosy, thalassemia and AIDS and Haemophilia and Leprosy, TB and AIDS and Haemophilia and Leprosy,Cancer and heart and kidney and thalassemia and TB ,Cancer and heart and kidney and thalassemia and AIDS ,Cancer and heart and kidney and thalassemia and Haemophilia ,Cancer and heart and kidney and thalassemia and Leprosy,Cancer and heart and kidney and TB and AIDS ,Cancer and heart and kidney and TB and Haemophilia ,Cancer and heart and kidney and TB and Leprosy,Cancer and heart and kidney and AIDS and Haemophilia ,Cancer and heart and kidney and AIDS and Leprosy,Cancer and heart and kidney and Haemophilia and Leprosy,Cancer and heart and thalassemia and TB and AIDS ,Cancer and heart and thalassemia and TB and Haemophilia ,Cancer and heart and thalassemia and TB and Leprosy,Cancer and heart and thalassemia and AIDS and Haemophilia ,Cancer and heart and thalassemia and AIDS and Leprosy,Cancer and heart and thalassemia and Haemophilia and Leprosy,Cancer and heart and TB and AIDS and Haemophilia ,Cancer and heart and TB and AIDS and Leprosy,Cancer and heart and TB and Haemophilia and Leprosy,Cancer and heart and AIDS and Haemophilia and Leprosy,Cancer and kidney and thalassemia and TB and AIDS ,Cancer and kidney and thalassemia and TB and Haemophilia ,Cancer and kidney and thalassemia and TB and Leprosy,Cancer and kidney and thalassemia and AIDS and Haemophilia ,Cancer and kidney and thalassemia and AIDS and Leprosy,Cancer and kidney and thalassemia and Haemophilia and Leprosy,Cancer and kidney and TB and AIDS and Haemophilia ,Cancer and kidney and TB and AIDS and Leprosy,Cancer and kidney and TB and Haemophilia and Leprosy,Cancer and kidney and AIDS and Haemophilia and Leprosy,Cancer and thalassemia and TB and AIDS and Haemophilia ,Cancer and thalassemia and TB and AIDS and Leprosy,Cancer and thalassemia and TB and Haemophilia and Leprosy,Cancer and thalassemia and AIDS and Haemophilia and Leprosy,Cancer and TB and AIDS and Haemophilia and Leprosy, heart and kidney and thalassemia and TB and AIDS , heart and kidney and thalassemia and TB and Haemophilia , heart and kidney and thalassemia and TB and Leprosy, heart and kidney and thalassemia and AIDS and Haemophilia , heart and kidney and thalassemia and AIDS and Leprosy, heart and kidney and thalassemia and Haemophilia and Leprosy, heart and kidney and TB and AIDS and Haemophilia , heart and kidney and TB and AIDS and Leprosy, heart and kidney and TB and Haemophilia and Leprosy, heart and kidney and AIDS and Haemophilia and Leprosy, heart and thalassemia and TB and AIDS and Haemophilia , heart and thalassemia and TB and AIDS and Leprosy, heart and thalassemia and TB and Haemophilia and Leprosy, heart and thalassemia and AIDS and Haemophilia and Leprosy, heart and TB and AIDS and Haemophilia and Leprosy, kidney and thalassemia and TB and AIDS and Haemophilia , kidney and thalassemia and TB and AIDS and Leprosy, kidney and thalassemia and TB and Haemophilia and Leprosy, kidney and thalassemia and AIDS and Haemophilia and Leprosy, kidney and TB and AIDS and Haemophilia and Leprosy, thalassemia and TB and AIDS and Haemophilia and Leprosy,Cancer and heart and kidney and thalassemia and TB and AIDS ,Cancer and heart and kidney and thalassemia and TB and Haemophilia ,Cancer and heart and kidney and thalassemia and TB and Leprosy,Cancer and heart and kidney and thalassemia and AIDS and Haemophilia ,Cancer and heart and kidney and thalassemia and AIDS and Leprosy,Cancer and heart and kidney and thalassemia and Haemophilia and Leprosy,Cancer and heart and kidney and TB and AIDS and Haemophilia ,Cancer and heart and kidney and TB and AIDS and Leprosy,Cancer and heart and kidney and TB and Haemophilia and Leprosy,Cancer and heart and kidney and AIDS and Haemophilia and Leprosy,Cancer and heart and thalassemia and TB and AIDS and Haemophilia ,Cancer and heart and thalassemia and TB and AIDS and Leprosy,Cancer and heart and thalassemia and TB and Haemophilia and Leprosy,Cancer and heart and thalassemia and AIDS and Haemophilia and Leprosy,Cancer and heart and TB and AIDS and Haemophilia and Leprosy,Cancer and kidney and thalassemia and TB and AIDS and Haemophilia ,Cancer and kidney and thalassemia and TB and AIDS and Leprosy,Cancer and kidney and thalassemia and TB and Haemophilia and Leprosy,Cancer and kidney and thalassemia and AIDS and Haemophilia and Leprosy,Cancer and kidney and TB and AIDS and Haemophilia and Leprosy,Cancer and thalassemia and TB and AIDS and Haemophilia and Leprosy, heart and kidney and thalassemia and TB and AIDS and Haemophilia , heart and kidney and thalassemia and TB and AIDS and Leprosy, heart and kidney and thalassemia and TB and Haemophilia and Leprosy, heart and kidney and thalassemia and AIDS and Haemophilia and Leprosy, heart and kidney and TB and AIDS and Haemophilia and Leprosy, heart and thalassemia and TB and AIDS and Haemophilia and Leprosy, kidney and thalassemia and TB and AIDS and Haemophilia and Leprosy,Cancer and heart and kidney and thalassemia and TB and AIDS and Haemophilia ,Cancer and heart and kidney and thalassemia and TB and AIDS and Leprosy,Cancer and heart and kidney and thalassemia and TB and Haemophilia and Leprosy,Cancer and heart and kidney and thalassemia and AIDS and Haemophilia and Leprosy,Cancer and heart and kidney and TB and AIDS and Haemophilia and Leprosy,Cancer and heart and thalassemia and TB and AIDS and Haemophilia and Leprosy,Cancer and kidney and thalassemia and TB and AIDS and Haemophilia and Leprosy, heart and kidney and thalassemia and TB and AIDS and Haemophilia and Leprosy,Cancer and heart and kidney and thalassemia and TB and AIDS and Haemophilia and Leprosy</v>
       </c>
     </row>
     <row r="7">
@@ -438,7 +438,7 @@
         <v>Select Widow Concession</v>
       </c>
       <c r="B8" t="str">
-        <v>war,IPKF,Parliamentary,Defence,Kargil,war,IPKF,Parliamentary,Defence,Kargil,war,IPKF,Parliamentary,Defence,Kargil,war,IPKF,Parliamentary,Defence,Kargil</v>
+        <v>War,IPKF,Parliamentary,Defence,Kargil</v>
       </c>
     </row>
     <row r="9">
@@ -446,31 +446,31 @@
         <v>Select Student Concession</v>
       </c>
       <c r="B9" t="str">
-        <v>General,SC,school rural,girls rural,exams,research,foreign,cadets,General,SC,school rural,girls rural,exams,research,foreign,cadets,General,SC,school rural,girls rural,exams,research,foreign,cadets,General,SC,school rural,girls rural,exams,research,foreign,cadets</v>
+        <v>General,SC,School rural,Girls rural,Exams,Research,Foreign,Cadets</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Select youth Concession</v>
+        <v>Select Youth Concession</v>
       </c>
       <c r="B10" t="str">
-        <v>project,seva,interview NonGov,interview st,scouts</v>
+        <v>Project,Seva,NonGov Interview ,State Interview,Scouts</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Select kisan Concession</v>
+        <v>Select Kisan Concession</v>
       </c>
       <c r="B11" t="str">
-        <v>agricultural,travel,training,conferences</v>
+        <v>Exihibition,Travel,Training,Conferences</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Select Artistists sportsman Concession</v>
+        <v>Select Artistists Sportsman Concession</v>
       </c>
       <c r="B12" t="str">
-        <v>performance,travel,state tour,nat tour,mounting,press</v>
+        <v>Performance,Travel,State tour,Nat tour,Mounting,Press</v>
       </c>
     </row>
     <row r="13">
@@ -483,23 +483,47 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Select Other Concessions</v>
+        <v>Gender Male, Select Widow Concession</v>
       </c>
       <c r="B14" t="str">
-        <v>Delegates,sewa,Social Service,tours,Ambulance Brigade</v>
+        <v>Infeasible Input</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Select Youth Concession</v>
+        <v>Passenger Type Senior Citizen, Select Student Concession</v>
       </c>
       <c r="B15" t="str">
-        <v>General,SC,school rural,girls rural,exams,research,foreign,cadets,General,SC,school rural,girls rural,exams,research,foreign,cadets</v>
+        <v>Infeasible Input</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Passenger Type Senior Citizen, Select Youth Concession</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Infeasible Input</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Passenger Type Child, Select Youth Concession</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Infeasible Input</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Gender Male, Select Nurse Concession</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Infeasible Input</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B18"/>
   </ignoredErrors>
 </worksheet>
 </file>